--- a/proofs/out/itil/release-management/release-schedule/release_schedule.xlsx
+++ b/proofs/out/itil/release-management/release-schedule/release_schedule.xlsx
@@ -413,268 +413,510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>meeting</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>releaser</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>security</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tsc-2024-01-10</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Announcements</t>
+          <t>22.11.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richard, Ulises did a release for Node.js 20</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>richardlau</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tsc-2024-01-10</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nodejs/node</t>
+          <t>22.12.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Requires a patch to V8, the V8 teams reluctant to accept the patch</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ruyadorno</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tsc-2024-01-10</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nodejs/node</t>
+          <t>22.13.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Feedback in the PR seems to be that we should wait until V8 accepts in upstream</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ruyadorno</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tsc-2024-01-10</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nodejs/node</t>
+          <t>22.13.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chengzhong, V8 team has discussed removing the API it uses, so there would be more we’d have to float.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tsc-2024-01-17</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nodejs/node</t>
+          <t>22.14.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ruy, concerned it’s too much scope to pull into the runtime, Ruy, maybe adding other package managers to other containers might be a better way than building into the runtime Itself. Anecdotal correlation: Yarn v1 is currently shipped with our Docker image and it’s also the leading package manager s</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tsc-2024-01-17</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nodejs/admin</t>
+          <t>22.15.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Claudio, learn section, moving a bunch of the guides over to new section. Plan is to release website mid this year,</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tsc-2024-02-07</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Announcements</t>
+          <t>22.16.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Security releases tomorrow!</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tsc-2025-02-05</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nodejs/TSC</t>
+          <t>22.17.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richard, new V8 landed last week, that invalidates caches, so that causes generally longer build times, that should now be resolved.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nodejs/TSC</t>
+          <t>22.17.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marco, added the agenda tag to this one. Something broke in corepack and we had to do a release in all LTS versions. We are still working on 20. Work around was for people to do corepack install which turned out not to be a huge issue. Based on how people could easily install corepack to address iss</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nodejs/security-wg</t>
+          <t>22.18.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Update on CVEs for EOL Release Lines – MITRE Removal &amp; Next Steps #1443</t>
+          <t>LTS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://github.com/nodejs/security-wg/issues/1443</t>
-        </is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Strategic Initiatives</t>
+          <t>22.19.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Zasso - V8 currency, please help me as there are many issues in the build System</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Strategic Initiatives</t>
+          <t>22.20.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richard found out why the V8 CI was broken and opened a PR to fix it</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>richardlau</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Strategic Initiatives</t>
+          <t>22.21.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chengzhong has identified issue related to workers planning to submit patch to v8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.21.1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>22.22.0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22.22.3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22.23.0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22.23.1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22.23.2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
